--- a/AAII_Financials/Quarterly/SNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="92">
   <si>
     <t>SNY</t>
   </si>
@@ -656,517 +656,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14052300</v>
+      </c>
+      <c r="E8" s="3">
         <v>14330200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12607200</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="3">
         <v>11559000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12243200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11229400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13439900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11559000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11802500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>27240300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14198200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22627000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10907500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>23030600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11661800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18971000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9070800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>19564000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10253400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>19368000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10518700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>23275800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12153100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20814000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10422500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>22557900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10792500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>18234500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8922300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>20619900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10542200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>20019700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>10449300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>21682600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>10910600</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3300600</v>
+      </c>
+      <c r="E9" s="3">
         <v>4262100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3513800</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="3">
         <v>3562200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3987400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3394300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4065400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3562200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3345300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8379000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4140200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6670100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3124800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7278600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3488100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5863400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2739800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6598800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3296400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6046900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3234900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7694400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3839100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6334900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3131700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7298500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3358200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5781000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2794400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6666900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3201000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6362800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3269100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>6728300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3258500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10751700</v>
+      </c>
+      <c r="E10" s="3">
         <v>10068100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9093400</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="3">
         <v>7996700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8255900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7835000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9374500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7996700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8457200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18861300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10058100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15957000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7782700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>15752000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8173700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13107600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6331000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>12965200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6957000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13321100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7283800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>15581400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8314000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>14479100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7290800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>15259400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7434200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>12453500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6127900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>13953100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>7341200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>13656900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7180200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>14954300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>7652100</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,124 +1219,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2551100</v>
+      </c>
+      <c r="E12" s="3">
         <v>2689900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2241900</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="3">
         <v>1779500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1948300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1733200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1760200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1779500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1698200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3941900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1876100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3424300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1615600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3283700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1555000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2817500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1292300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2830600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1371100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2936700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1513000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3555900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1666000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3496300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1656700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3713100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1618200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3025000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1405400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>3147200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1504600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2992300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1536500</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>3120000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1433200</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1439,240 +1455,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1790200</v>
+      </c>
+      <c r="E14" s="3">
         <v>3358000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>323000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>-296900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2560600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>454700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>281500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-296900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>389000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2118200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>956400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>195300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>549600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>187400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>551200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>161300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>337100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>116200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1179300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>170500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2427000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>416500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3043300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>390000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1762500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>331200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>777400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>213000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>728200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>300700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>428600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>139700</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>1017700</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>98600</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>630600</v>
+      </c>
+      <c r="E15" s="3">
         <v>631700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>443900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>723700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>864100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>816600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>596100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>488400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>481900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>594800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>596100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>531300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1266000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>497100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>990200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>487200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>872700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>414600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>820000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>397100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>795900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>419300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>963300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>516000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1202400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>637000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1312900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>666300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1385200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>594800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>1096900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>502900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>982900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>486900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>1110800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>590400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>956700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>473000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,240 +1735,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>11096800</v>
+      </c>
+      <c r="E17" s="3">
         <v>12287200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10596600</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G17" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="3">
         <v>9871200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10468100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9304800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9759700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9871200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8737500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19678700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11254400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18460700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8306800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18138100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8396600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15166400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6970000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15569400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7633800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8341100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8208600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>20925800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9541400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19505900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8737000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>19584100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7786400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>15860600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7603700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>17564800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8325200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>16570700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8451400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>17610700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8104000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2955600</v>
+      </c>
+      <c r="E18" s="3">
         <v>2043000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2010600</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G18" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="3">
         <v>1687800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1775100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1924500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3680100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1687800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3065000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7561600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2943800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4166300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2600700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4892500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3265200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3804600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2100800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3994600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2619700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11026900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2310100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2350000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2611700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1308200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1685400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2973800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3006000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2373900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1318700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3055200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2217100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3449000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1997800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4071900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2806600</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1984,588 +2016,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E20" s="3">
         <v>133800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-23500</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="3">
         <v>152800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-38500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-54400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-68800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>152800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>154000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-55100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>22900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-84600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-91500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>29600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-86800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>47900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-78900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>82900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-84700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>136600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-98000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>145900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-64600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>110000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-117400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>117500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>33700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-86400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>56100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-74000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-23500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-286400</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3468500</v>
+      </c>
+      <c r="E21" s="3">
         <v>2540800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2478000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>723700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>864100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>816600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2131000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2302000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2460800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4343800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2131000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3609300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11503500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R21" s="3">
         <v>5681000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-632600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8533000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="3">
         <v>5237100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X21" s="3">
         <v>7703900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z21" s="3">
         <v>13305800</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3">
         <v>6774500</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD21" s="3">
         <v>5899600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF21" s="3">
         <v>6041100</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH21" s="3">
         <v>4444700</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>5247500</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL21" s="3">
         <v>5482000</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN21" s="3">
         <v>6078000</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AO21" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>174800</v>
+      </c>
+      <c r="E22" s="3">
         <v>-66900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>72800</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="3">
         <v>65500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>109000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>92000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>336600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>65500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>182500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>241500</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="3">
         <v>191500</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T22" s="3">
         <v>188600</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V22" s="3">
         <v>198900</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X22" s="3">
         <v>215400</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z22" s="3">
         <v>265100</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB22" s="3">
         <v>315200</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD22" s="3">
         <v>322300</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF22" s="3">
         <v>306400</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH22" s="3">
         <v>232800</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>200800</v>
       </c>
-      <c r="AJ22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL22" s="3">
         <v>187400</v>
       </c>
-      <c r="AL22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM22" s="3">
+      <c r="AM22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN22" s="3">
         <v>199500</v>
       </c>
-      <c r="AN22" s="3" t="s">
+      <c r="AO22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>946000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1356100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1722800</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G23" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="3">
         <v>1875500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4358200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1445700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3282200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1875500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2681400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7474100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2888700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3997700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2516100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4711500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3173600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3635300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2014000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3827000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2540800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10844700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2225500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2171400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2513700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1131700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1620900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2777400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2888600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2258600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1320900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2888000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2130700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3317700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1923900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3848900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2520200</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>515300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-408600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>270100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="3">
         <v>295900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>972500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>170400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>595900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>295900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>498700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1673600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>649500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>538600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>360200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>949700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>652600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>717300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>412400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>810900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>508600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1084400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>490000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>147100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>328300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>15300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>305000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>217700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>472900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>326100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>205300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1245400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>461100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>686700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>394400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>973100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>540000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2680,240 +2728,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>430700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-947500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1452700</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G26" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="3">
         <v>1579700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3385700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1275400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2686300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1579700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2182700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5800500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2239200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3459100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2155900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3761800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2521000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2918000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1601600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3016100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2032200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9760400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1735400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2024300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2185400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1116400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1315800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2559800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2415700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1932500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1115600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1642600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1669500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2631100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1529500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2875800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1980200</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-940500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4627100</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G27" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="3">
         <v>1566600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3324800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1228300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2672500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1566600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2167500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5745100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2243500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3464500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2179800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3736900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2487600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2924300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1598600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3005200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2026000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10124700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1900300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2167900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2285800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1235200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1360100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3005700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2523100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1952200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1116700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1643700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1680700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2589600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1489600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2859400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1953200</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3028,20 +3085,23 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>15300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>3179100</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
@@ -3084,14 +3144,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>16</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -3103,49 +3163,52 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-117900</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-122500</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-1089500</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>70700</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>4960300</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>5196500</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>32900</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3260,8 +3323,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3376,240 +3442,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-117700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-133800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>23500</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="3">
         <v>-152800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>38500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>54400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>68800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-152800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-154000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>55100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-22900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>84600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>91500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-29600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>86800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-47900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>78900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-82900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>84700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-136600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>98000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-145900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>64600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-110000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>117400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-117500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-33700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>86400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-56100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>74000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>23500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>286400</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-940500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4627100</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G33" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="3">
         <v>1566600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3324800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1228300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2672500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1566600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2167500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5745100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2243500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3464500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2179800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3736900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2487600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2924300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1598600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3005200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2026000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10124700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1900300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2050000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2163300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1235200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1360100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2990400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2518700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1952200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1115600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>554300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1751400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>7549900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>6686000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2892300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1965000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3724,245 +3799,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-940500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4627100</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G35" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="3">
         <v>1566600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3324800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1228300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2672500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1566600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2167500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5745100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2243500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3464500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2179800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3736900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2487600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2924300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1598600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3005200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2026000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10124700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1900300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2050000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2163300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1235200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1360100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2990400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2518700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1952200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1115600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>554300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1751400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>7549900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>6686000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2892300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1965000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4003,8 +4087,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4045,44 +4130,45 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7254700</v>
+      </c>
+      <c r="E41" s="3">
         <v>8990300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18037600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7703700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7280600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9627500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8726000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13611200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7212000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N41" s="3">
         <v>8726000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>16</v>
       </c>
@@ -4119,71 +4205,74 @@
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB41" s="3">
         <v>11005200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD41" s="3">
         <v>7931300</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF41" s="3">
         <v>8191600</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH41" s="3">
         <v>8227300</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>11573300</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL41" s="3">
         <v>12203900</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM41" s="3">
+      <c r="AM41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN41" s="3">
         <v>12058600</v>
       </c>
-      <c r="AN41" s="3" t="s">
+      <c r="AO41" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>20000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>119100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>123800</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -4199,11 +4288,11 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -4277,44 +4366,47 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10517500</v>
+      </c>
+      <c r="E43" s="3">
         <v>12969400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9638300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11004200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9434300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12202900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9434500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11484500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8787400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N43" s="3">
         <v>9434500</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>16</v>
       </c>
@@ -4351,86 +4443,89 @@
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB43" s="3">
         <v>9265700</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD43" s="3">
         <v>8504200</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF43" s="3">
         <v>8587900</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH43" s="3">
         <v>7249000</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>8096300</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL43" s="3">
         <v>7693500</v>
       </c>
-      <c r="AL43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM43" s="3">
+      <c r="AM43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN43" s="3">
         <v>8581700</v>
       </c>
-      <c r="AN43" s="3" t="s">
+      <c r="AO43" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12712200</v>
+      </c>
+      <c r="E44" s="3">
         <v>11992500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11295400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9764000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11367200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10684200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10884300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9575700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9790900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N44" s="3">
         <v>10884300</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>16</v>
       </c>
@@ -4467,86 +4562,89 @@
       <c r="Z44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB44" s="3">
         <v>9332300</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD44" s="3">
         <v>9908800</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF44" s="3">
         <v>8844500</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH44" s="3">
         <v>8085700</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>7649700</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL44" s="3">
         <v>8129900</v>
       </c>
-      <c r="AL44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM44" s="3">
+      <c r="AM44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN44" s="3">
         <v>8089900</v>
       </c>
-      <c r="AN44" s="3" t="s">
+      <c r="AO44" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5528400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1291500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4501500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14574000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4148700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>413400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3971600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1020600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4155300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N45" s="3">
         <v>3971600</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4583,86 +4681,89 @@
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB45" s="3">
         <v>3797600</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD45" s="3">
         <v>3435100</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF45" s="3">
         <v>3450500</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH45" s="3">
         <v>2719700</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>2249600</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL45" s="3">
         <v>2346100</v>
       </c>
-      <c r="AL45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM45" s="3">
+      <c r="AM45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN45" s="3">
         <v>2595300</v>
       </c>
-      <c r="AN45" s="3" t="s">
+      <c r="AO45" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36012800</v>
+      </c>
+      <c r="E46" s="3">
         <v>36341400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43472700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44091500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>32230800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33900700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>33016400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36455100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29945600</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N46" s="3">
         <v>33016400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4699,86 +4800,89 @@
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB46" s="3">
         <v>33400800</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD46" s="3">
         <v>29779400</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF46" s="3">
         <v>29074500</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH46" s="3">
         <v>26281700</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>29568900</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK46" s="3">
+      <c r="AK46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL46" s="3">
         <v>30373400</v>
       </c>
-      <c r="AL46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM46" s="3">
+      <c r="AM46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN46" s="3">
         <v>31325500</v>
       </c>
-      <c r="AN46" s="3" t="s">
+      <c r="AO46" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8045100</v>
+        <v>8116100</v>
       </c>
       <c r="E47" s="3">
+        <v>8047400</v>
+      </c>
+      <c r="F47" s="3">
         <v>8214900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3374100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2828700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2946800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2783800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2955000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2770200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N47" s="3">
         <v>2783800</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4815,86 +4919,89 @@
       <c r="Z47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB47" s="3">
         <v>6990500</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD47" s="3">
         <v>6737200</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF47" s="3">
         <v>7447500</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH47" s="3">
         <v>6629700</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>9734400</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL47" s="3">
         <v>6439100</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN47" s="3">
         <v>6667200</v>
       </c>
-      <c r="AN47" s="3" t="s">
+      <c r="AO47" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13657000</v>
+      </c>
+      <c r="E48" s="3">
         <v>13515300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12926600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12010600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12729000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13058500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12584100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12486900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12170200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N48" s="3">
         <v>12584100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4931,88 +5038,91 @@
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB48" s="3">
         <v>12861400</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD48" s="3">
         <v>12600400</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF48" s="3">
         <v>11416200</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH48" s="3">
         <v>10398100</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>10747500</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL48" s="3">
         <v>10808100</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN48" s="3">
         <v>11760400</v>
       </c>
-      <c r="AN48" s="3" t="s">
+      <c r="AO48" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>68875800</v>
+      </c>
+      <c r="E49" s="3">
         <v>69073600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>61850900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>59679100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>73077300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>74814900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>74893000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>69793700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>68151800</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>74893000</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>16</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>16</v>
@@ -5047,50 +5157,53 @@
       <c r="Z49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB49" s="3">
         <v>71318200</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD49" s="3">
         <v>74720200</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF49" s="3">
         <v>78218100</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH49" s="3">
         <v>73855900</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>59851400</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL49" s="3">
         <v>61499600</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN49" s="3">
         <v>60059200</v>
       </c>
-      <c r="AN49" s="3" t="s">
+      <c r="AO49" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5205,8 +5318,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5321,44 +5437,47 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1089600</v>
+        <v>1123000</v>
       </c>
       <c r="E52" s="3">
+        <v>1087200</v>
+      </c>
+      <c r="F52" s="3">
         <v>981800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>898600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>589300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>633400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>843900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>851800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>959600</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N52" s="3">
         <v>843900</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>16</v>
       </c>
@@ -5395,50 +5514,53 @@
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB52" s="3">
         <v>7038300</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD52" s="3">
         <v>6207900</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF52" s="3">
         <v>5628200</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH52" s="3">
         <v>6664900</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>4912100</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL52" s="3">
         <v>5176900</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM52" s="3">
+      <c r="AM52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN52" s="3">
         <v>13052800</v>
       </c>
-      <c r="AN52" s="3" t="s">
+      <c r="AO52" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5553,44 +5675,47 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>147446600</v>
+      </c>
+      <c r="E54" s="3">
         <v>148884600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>146751600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>137486300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>139028200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>139785600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>136848300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>135430200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>127353100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N54" s="3">
         <v>136848300</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5627,50 +5752,53 @@
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB54" s="3">
         <v>131609100</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD54" s="3">
         <v>130045100</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF54" s="3">
         <v>131784500</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH54" s="3">
         <v>123830200</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>111989200</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL54" s="3">
         <v>114297100</v>
       </c>
-      <c r="AL54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM54" s="3">
+      <c r="AM54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN54" s="3">
         <v>122865000</v>
       </c>
-      <c r="AN54" s="3" t="s">
+      <c r="AO54" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5711,8 +5839,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5753,44 +5882,45 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8168600</v>
+      </c>
+      <c r="E57" s="3">
         <v>8642700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8308900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7817600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7964200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8099900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8040400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7281200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6855500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N57" s="3">
         <v>8040400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>16</v>
       </c>
@@ -5827,88 +5957,91 @@
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB57" s="3">
         <v>6202400</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD57" s="3">
         <v>5978500</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF57" s="3">
         <v>5963000</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH57" s="3">
         <v>5031000</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>5198200</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL57" s="3">
         <v>4827900</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN57" s="3">
         <v>5043900</v>
       </c>
-      <c r="AN57" s="3" t="s">
+      <c r="AO57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8286300</v>
+      </c>
+      <c r="E58" s="3">
         <v>5417400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8879600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4635100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10195000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2565500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5400700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4756900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3443400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>5400700</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>16</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>16</v>
@@ -5943,86 +6076,89 @@
       <c r="Z58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB58" s="3">
         <v>5618700</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD58" s="3">
         <v>5456100</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF58" s="3">
         <v>3090900</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH58" s="3">
         <v>6757100</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>1430500</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK58" s="3">
+      <c r="AK58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL58" s="3">
         <v>3638600</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM58" s="3">
+      <c r="AM58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN58" s="3">
         <v>1226600</v>
       </c>
-      <c r="AN58" s="3" t="s">
+      <c r="AO58" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>16496400</v>
+        <v>20024000</v>
       </c>
       <c r="E59" s="3">
+        <v>16323800</v>
+      </c>
+      <c r="F59" s="3">
         <v>16938300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15289400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14013700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13327100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13629900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10828300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12779600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N59" s="3">
         <v>13629900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>16</v>
       </c>
@@ -6059,86 +6195,89 @@
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB59" s="3">
         <v>11971800</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD59" s="3">
         <v>11159300</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF59" s="3">
         <v>11500200</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH59" s="3">
         <v>9740400</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>21049700</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL59" s="3">
         <v>10669000</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN59" s="3">
         <v>13019900</v>
       </c>
-      <c r="AN59" s="3" t="s">
+      <c r="AO59" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36478900</v>
+      </c>
+      <c r="E60" s="3">
         <v>33280500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34126800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30191500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32172900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26756900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27071000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25621500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23078600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N60" s="3">
         <v>27071000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>16</v>
       </c>
@@ -6175,86 +6314,89 @@
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB60" s="3">
         <v>23793000</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD60" s="3">
         <v>22593900</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF60" s="3">
         <v>20554100</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH60" s="3">
         <v>21528500</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>17349300</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK60" s="3">
+      <c r="AK60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL60" s="3">
         <v>19135500</v>
       </c>
-      <c r="AL60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM60" s="3">
+      <c r="AM60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN60" s="3">
         <v>19290400</v>
       </c>
-      <c r="AN60" s="3" t="s">
+      <c r="AO60" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18451300</v>
+        <v>18648500</v>
       </c>
       <c r="E61" s="3">
+        <v>18546400</v>
+      </c>
+      <c r="F61" s="3">
         <v>17291800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13910300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15253400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17798200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17554600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17912800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18757100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>17554600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -6292,85 +6434,88 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>24711700</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>25987900</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>26107800</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>25070600</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>16054600</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>17001500</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
       <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>19748200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9308400</v>
+        <v>5820900</v>
       </c>
       <c r="E62" s="3">
+        <v>9213300</v>
+      </c>
+      <c r="F62" s="3">
         <v>8781000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8474000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9273500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8545400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8374500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7432900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7380300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N62" s="3">
         <v>8374500</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>16</v>
       </c>
@@ -6407,50 +6552,53 @@
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB62" s="3">
         <v>14101100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD62" s="3">
         <v>14975600</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF62" s="3">
         <v>15290200</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH62" s="3">
         <v>15346700</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>13241700</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL62" s="3">
         <v>13318000</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN62" s="3">
         <v>16069500</v>
       </c>
-      <c r="AN62" s="3" t="s">
+      <c r="AO62" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6565,8 +6713,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6681,8 +6832,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6797,44 +6951,47 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67968700</v>
+      </c>
+      <c r="E66" s="3">
         <v>64688300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>64216100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>56880600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60814300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>57600300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57211800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55113800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52814100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N66" s="3">
         <v>57211800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6871,50 +7028,53 @@
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB66" s="3">
         <v>62809000</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD66" s="3">
         <v>63751500</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF66" s="3">
         <v>62140100</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH66" s="3">
         <v>62125900</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>46835200</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL66" s="3">
         <v>49635700</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM66" s="3">
+      <c r="AM66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN66" s="3">
         <v>55307600</v>
       </c>
-      <c r="AN66" s="3" t="s">
+      <c r="AO66" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6955,8 +7115,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7071,8 +7232,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7187,8 +7351,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7303,8 +7470,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7419,8 +7589,11 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7496,8 +7669,8 @@
       <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB72" s="3">
-        <v>0</v>
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC72" s="3">
         <v>0</v>
@@ -7535,8 +7708,11 @@
       <c r="AN72" s="3">
         <v>0</v>
       </c>
+      <c r="AO72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7651,8 +7827,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7767,8 +7946,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7883,47 +8065,50 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>79066600</v>
+      </c>
+      <c r="E76" s="3">
         <v>83804200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>82217300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>80243300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>77884900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>81839300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>79289300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>79923100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74170000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>76872400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>79289300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>81251600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7957,50 +8142,53 @@
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB76" s="3">
         <v>68800100</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD76" s="3">
         <v>66293700</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF76" s="3">
         <v>69644400</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH76" s="3">
         <v>61704300</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>65154000</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL76" s="3">
         <v>64661400</v>
       </c>
-      <c r="AL76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM76" s="3">
+      <c r="AM76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN76" s="3">
         <v>67557500</v>
       </c>
-      <c r="AN76" s="3" t="s">
+      <c r="AO76" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8115,245 +8303,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-940500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4627100</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G81" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="3">
         <v>1566600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3324800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1228300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2672500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1566600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2167500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5745100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2243500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3464500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2179800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3736900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2487600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2924300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1598600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3005200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2026000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10124700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1900300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2050000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2163300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1235200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1360100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2990400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2518700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1952200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1115600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>554300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1751400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>7549900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>6686000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2892300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1965000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8394,8 +8591,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8432,86 +8630,89 @@
       <c r="N83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P83" s="3">
         <v>3788000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T83" s="3">
         <v>3632800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X83" s="3">
         <v>3674400</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2196000</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB83" s="3">
         <v>4287900</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD83" s="3">
         <v>4445600</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF83" s="3">
         <v>2957300</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1953300</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>2158700</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL83" s="3">
         <v>1976900</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN83" s="3">
         <v>2029500</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AO83" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8626,8 +8827,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8742,8 +8946,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8858,8 +9065,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8974,8 +9184,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9090,20 +9303,23 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3381700</v>
+      </c>
+      <c r="E89" s="3">
         <v>4044900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1717000</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
@@ -9128,86 +9344,89 @@
       <c r="N89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P89" s="3">
         <v>11658600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T89" s="3">
         <v>11406900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X89" s="3">
         <v>7429600</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z89" s="3">
         <v>4282900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB89" s="3">
         <v>5329200</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD89" s="3">
         <v>3739800</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF89" s="3">
         <v>4461900</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH89" s="3">
         <v>1949000</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>9377600</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL89" s="3">
         <v>2867800</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN89" s="3">
         <v>6161300</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AO89" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9248,20 +9467,21 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1007700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2068800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-992400</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G91" s="3" t="s">
         <v>16</v>
       </c>
@@ -9286,86 +9506,89 @@
       <c r="N91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P91" s="3">
         <v>-991000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1401000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-682000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>16</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X91" s="3">
         <v>-2077600</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-744000</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-1138200</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-989400</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-1365100</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-903700</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-1074900</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-1119700</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-1036500</v>
       </c>
-      <c r="AN91" s="3" t="s">
+      <c r="AO91" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9480,8 +9703,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9596,20 +9822,23 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-417000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2502100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11160300</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>16</v>
       </c>
@@ -9634,86 +9863,89 @@
       <c r="N94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P94" s="3">
         <v>-2298300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T94" s="3">
         <v>-7911800</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X94" s="3">
         <v>3609600</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z94" s="3">
         <v>8809100</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-1042500</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-194100</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF94" s="3">
         <v>247200</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-14362900</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-2971000</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL94" s="3">
         <v>3688000</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-1369800</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AO94" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9754,20 +9986,21 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5624400</v>
+      </c>
+      <c r="E96" s="3">
         <v>5602900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5604200</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>16</v>
       </c>
@@ -9792,12 +10025,12 @@
       <c r="N96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P96" s="3">
         <v>-4616500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -9805,11 +10038,11 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-4345100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -9817,17 +10050,17 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-3926800</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-4294900</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -9835,11 +10068,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-4510300</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -9847,11 +10080,11 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4142800</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
@@ -9859,19 +10092,22 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-4162600</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9986,8 +10222,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10102,8 +10341,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10218,20 +10460,23 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2062200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3017500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4576600</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>16</v>
       </c>
@@ -10256,86 +10501,89 @@
       <c r="N100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P100" s="3">
         <v>-6447300</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T100" s="3">
         <v>-7649400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X100" s="3">
         <v>-6468100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-5893100</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-1148700</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-3775100</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-5392800</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH100" s="3">
         <v>9325300</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-3040600</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-5825400</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN100" s="3">
         <v>132600</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AO100" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10372,98 +10620,101 @@
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P101" s="3">
         <v>8900</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T101" s="3">
         <v>16300</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X101" s="3">
         <v>-63800</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-62200</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD101" s="3">
         <v>14100</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF101" s="3">
         <v>11800</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-9900</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-30300</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-52700</v>
       </c>
-      <c r="AL101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN101" s="3">
         <v>2300</v>
       </c>
-      <c r="AN101" s="3" t="s">
+      <c r="AO101" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>914000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1466500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8274800</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
@@ -10476,8 +10727,8 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>16</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>16</v>
@@ -10488,82 +10739,85 @@
       <c r="N102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P102" s="3">
         <v>2921800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T102" s="3">
         <v>-4138000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X102" s="3">
         <v>4476300</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z102" s="3">
         <v>7136700</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB102" s="3">
         <v>3134500</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-215300</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-671900</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-3098600</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-630600</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL102" s="3">
         <v>677700</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN102" s="3">
         <v>4926500</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AO102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
